--- a/dictionaries/urban_ath/1_3/1_3_trimester_rep.xlsx
+++ b/dictionaries/urban_ath/1_3/1_3_trimester_rep.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\PROJECTS\ATHLETE\DOCUMENTS\dictionaries\jose_dictionaries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/demetrisavraam/Desktop/GitHub/ds-dictionaries/dictionaries/urban_ath/1_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F9EC3B-C949-41BD-AEE5-4758A5926631}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904FA3F5-2E5C-0C45-A121-79ACE858C14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="16380" windowHeight="8190" tabRatio="256" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="256" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="2" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="361">
   <si>
     <t>name</t>
   </si>
@@ -1116,13 +1116,43 @@
   </si>
   <si>
     <t>number of facilities related to supermarket establishments divided by the area of the 800 meters buffer at trimester</t>
+  </si>
+  <si>
+    <t>urb_deg_</t>
+  </si>
+  <si>
+    <t>Urban degree at trimester as classified by GHS-SMOD</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>dense town</t>
+  </si>
+  <si>
+    <t>semi-dense town</t>
+  </si>
+  <si>
+    <t>peri-urban area</t>
+  </si>
+  <si>
+    <t>village</t>
+  </si>
+  <si>
+    <t>rural dispersed area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mostly uninahbitated area </t>
+  </si>
+  <si>
+    <t xml:space="preserve">water </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1287,6 +1317,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1513,7 +1549,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1556,6 +1592,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1570,19 +1607,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="20% - Accent2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -1620,6 +1655,7 @@
     <cellStyle name="Linked Cell" xfId="35" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
     <cellStyle name="Neutral" xfId="36" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{8E286D8E-01FB-E14C-8BD9-0F9678775C2E}"/>
     <cellStyle name="Note" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
     <cellStyle name="Output" xfId="38" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
     <cellStyle name="Title" xfId="39" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
@@ -2089,15 +2125,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AMH127"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="26" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.7109375" style="1"/>
+    <col min="5" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2111,7 +2147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2125,7 +2161,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2136,7 +2172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2147,21 +2183,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2175,7 +2211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2186,7 +2222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2200,7 +2236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -2214,7 +2250,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2228,7 +2264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2242,7 +2278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2256,7 +2292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -2270,7 +2306,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2284,7 +2320,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -2298,7 +2334,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2312,7 +2348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -2326,7 +2362,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -2340,7 +2376,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -2354,7 +2390,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -2368,7 +2404,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -2382,7 +2418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2396,7 +2432,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2410,7 +2446,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2424,7 +2460,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -2438,7 +2474,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -2452,7 +2488,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -2466,7 +2502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -2480,7 +2516,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -2494,7 +2530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -2508,7 +2544,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -2522,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -2536,7 +2572,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -2550,7 +2586,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -2564,7 +2600,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -2578,31 +2614,31 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11" t="s">
+      <c r="C36"/>
+      <c r="D36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11" t="s">
+      <c r="C37"/>
+      <c r="D37" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -2616,7 +2652,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2630,7 +2666,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2644,7 +2680,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2658,7 +2694,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2672,7 +2708,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2686,7 +2722,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2700,7 +2736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -2714,7 +2750,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2728,7 +2764,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2742,7 +2778,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>108</v>
       </c>
@@ -2756,7 +2792,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>111</v>
       </c>
@@ -2770,7 +2806,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>113</v>
       </c>
@@ -2784,7 +2820,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -2798,7 +2834,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -2812,7 +2848,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>121</v>
       </c>
@@ -2826,7 +2862,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>123</v>
       </c>
@@ -2840,7 +2876,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>125</v>
       </c>
@@ -2854,7 +2890,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -2868,7 +2904,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>129</v>
       </c>
@@ -2882,7 +2918,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>131</v>
       </c>
@@ -2896,7 +2932,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>133</v>
       </c>
@@ -2908,7 +2944,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>135</v>
       </c>
@@ -2920,7 +2956,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>137</v>
       </c>
@@ -2932,7 +2968,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>139</v>
       </c>
@@ -2946,7 +2982,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>141</v>
       </c>
@@ -2960,7 +2996,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>143</v>
       </c>
@@ -2974,7 +3010,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>145</v>
       </c>
@@ -2988,7 +3024,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>147</v>
       </c>
@@ -3002,7 +3038,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>149</v>
       </c>
@@ -3016,7 +3052,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>151</v>
       </c>
@@ -3030,7 +3066,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -3044,7 +3080,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>155</v>
       </c>
@@ -3058,7 +3094,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>157</v>
       </c>
@@ -3072,7 +3108,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>159</v>
       </c>
@@ -3086,7 +3122,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>161</v>
       </c>
@@ -3100,7 +3136,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>163</v>
       </c>
@@ -3112,7 +3148,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>165</v>
       </c>
@@ -3124,7 +3160,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>167</v>
       </c>
@@ -3138,7 +3174,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>170</v>
       </c>
@@ -3152,7 +3188,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>173</v>
       </c>
@@ -3166,7 +3202,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>175</v>
       </c>
@@ -3180,7 +3216,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>178</v>
       </c>
@@ -3194,7 +3230,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>181</v>
       </c>
@@ -3208,7 +3244,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>183</v>
       </c>
@@ -3220,7 +3256,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>185</v>
       </c>
@@ -3232,7 +3268,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>187</v>
       </c>
@@ -3246,7 +3282,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>189</v>
       </c>
@@ -3260,7 +3296,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>307</v>
       </c>
@@ -3274,7 +3310,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>308</v>
       </c>
@@ -3288,7 +3324,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>309</v>
       </c>
@@ -3302,7 +3338,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>310</v>
       </c>
@@ -3316,7 +3352,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>311</v>
       </c>
@@ -3330,7 +3366,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>312</v>
       </c>
@@ -3344,7 +3380,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>313</v>
       </c>
@@ -3358,7 +3394,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>314</v>
       </c>
@@ -3372,7 +3408,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>315</v>
       </c>
@@ -3386,7 +3422,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>316</v>
       </c>
@@ -3400,7 +3436,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>317</v>
       </c>
@@ -3414,7 +3450,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>318</v>
       </c>
@@ -3428,7 +3464,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>319</v>
       </c>
@@ -3442,7 +3478,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>320</v>
       </c>
@@ -3456,7 +3492,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
         <v>321</v>
       </c>
@@ -3470,7 +3506,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>322</v>
       </c>
@@ -3484,7 +3520,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>323</v>
       </c>
@@ -3498,7 +3534,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>324</v>
       </c>
@@ -3512,7 +3548,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>325</v>
       </c>
@@ -3526,7 +3562,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>326</v>
       </c>
@@ -3540,7 +3576,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
         <v>327</v>
       </c>
@@ -3554,7 +3590,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
         <v>328</v>
       </c>
@@ -3568,7 +3604,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
         <v>191</v>
       </c>
@@ -3582,7 +3618,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>194</v>
       </c>
@@ -3596,7 +3632,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>196</v>
       </c>
@@ -3610,7 +3646,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>198</v>
       </c>
@@ -3624,7 +3660,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>200</v>
       </c>
@@ -3638,7 +3674,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>202</v>
       </c>
@@ -3652,7 +3688,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>204</v>
       </c>
@@ -3666,7 +3702,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>206</v>
       </c>
@@ -3680,7 +3716,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>208</v>
       </c>
@@ -3694,7 +3730,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>210</v>
       </c>
@@ -3708,7 +3744,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>212</v>
       </c>
@@ -3722,7 +3758,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>215</v>
       </c>
@@ -3736,7 +3772,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>218</v>
       </c>
@@ -3750,7 +3786,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>221</v>
       </c>
@@ -3764,7 +3800,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>224</v>
       </c>
@@ -3778,7 +3814,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>226</v>
       </c>
@@ -3792,7 +3828,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>228</v>
       </c>
@@ -3806,7 +3842,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>230</v>
       </c>
@@ -3820,7 +3856,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
         <v>232</v>
       </c>
@@ -3834,14 +3870,1039 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C127"/>
+    <row r="127" spans="1:1022" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F127" s="7"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="7"/>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7"/>
+      <c r="M127" s="7"/>
+      <c r="N127" s="7"/>
+      <c r="O127" s="7"/>
+      <c r="P127" s="7"/>
+      <c r="Q127" s="7"/>
+      <c r="R127" s="7"/>
+      <c r="S127" s="7"/>
+      <c r="T127" s="7"/>
+      <c r="U127" s="7"/>
+      <c r="V127" s="7"/>
+      <c r="W127" s="7"/>
+      <c r="X127" s="7"/>
+      <c r="Y127" s="7"/>
+      <c r="Z127" s="7"/>
+      <c r="AA127" s="7"/>
+      <c r="AB127" s="7"/>
+      <c r="AC127" s="7"/>
+      <c r="AD127" s="7"/>
+      <c r="AE127" s="7"/>
+      <c r="AF127" s="7"/>
+      <c r="AG127" s="7"/>
+      <c r="AH127" s="7"/>
+      <c r="AI127" s="7"/>
+      <c r="AJ127" s="7"/>
+      <c r="AK127" s="7"/>
+      <c r="AL127" s="7"/>
+      <c r="AM127" s="7"/>
+      <c r="AN127" s="7"/>
+      <c r="AO127" s="7"/>
+      <c r="AP127" s="7"/>
+      <c r="AQ127" s="7"/>
+      <c r="AR127" s="7"/>
+      <c r="AS127" s="7"/>
+      <c r="AT127" s="7"/>
+      <c r="AU127" s="7"/>
+      <c r="AV127" s="7"/>
+      <c r="AW127" s="7"/>
+      <c r="AX127" s="7"/>
+      <c r="AY127" s="7"/>
+      <c r="AZ127" s="7"/>
+      <c r="BA127" s="7"/>
+      <c r="BB127" s="7"/>
+      <c r="BC127" s="7"/>
+      <c r="BD127" s="7"/>
+      <c r="BE127" s="7"/>
+      <c r="BF127" s="7"/>
+      <c r="BG127" s="7"/>
+      <c r="BH127" s="7"/>
+      <c r="BI127" s="7"/>
+      <c r="BJ127" s="7"/>
+      <c r="BK127" s="7"/>
+      <c r="BL127" s="7"/>
+      <c r="BM127" s="7"/>
+      <c r="BN127" s="7"/>
+      <c r="BO127" s="7"/>
+      <c r="BP127" s="7"/>
+      <c r="BQ127" s="7"/>
+      <c r="BR127" s="7"/>
+      <c r="BS127" s="7"/>
+      <c r="BT127" s="7"/>
+      <c r="BU127" s="7"/>
+      <c r="BV127" s="7"/>
+      <c r="BW127" s="7"/>
+      <c r="BX127" s="7"/>
+      <c r="BY127" s="7"/>
+      <c r="BZ127" s="7"/>
+      <c r="CA127" s="7"/>
+      <c r="CB127" s="7"/>
+      <c r="CC127" s="7"/>
+      <c r="CD127" s="7"/>
+      <c r="CE127" s="7"/>
+      <c r="CF127" s="7"/>
+      <c r="CG127" s="7"/>
+      <c r="CH127" s="7"/>
+      <c r="CI127" s="7"/>
+      <c r="CJ127" s="7"/>
+      <c r="CK127" s="7"/>
+      <c r="CL127" s="7"/>
+      <c r="CM127" s="7"/>
+      <c r="CN127" s="7"/>
+      <c r="CO127" s="7"/>
+      <c r="CP127" s="7"/>
+      <c r="CQ127" s="7"/>
+      <c r="CR127" s="7"/>
+      <c r="CS127" s="7"/>
+      <c r="CT127" s="7"/>
+      <c r="CU127" s="7"/>
+      <c r="CV127" s="7"/>
+      <c r="CW127" s="7"/>
+      <c r="CX127" s="7"/>
+      <c r="CY127" s="7"/>
+      <c r="CZ127" s="7"/>
+      <c r="DA127" s="7"/>
+      <c r="DB127" s="7"/>
+      <c r="DC127" s="7"/>
+      <c r="DD127" s="7"/>
+      <c r="DE127" s="7"/>
+      <c r="DF127" s="7"/>
+      <c r="DG127" s="7"/>
+      <c r="DH127" s="7"/>
+      <c r="DI127" s="7"/>
+      <c r="DJ127" s="7"/>
+      <c r="DK127" s="7"/>
+      <c r="DL127" s="7"/>
+      <c r="DM127" s="7"/>
+      <c r="DN127" s="7"/>
+      <c r="DO127" s="7"/>
+      <c r="DP127" s="7"/>
+      <c r="DQ127" s="7"/>
+      <c r="DR127" s="7"/>
+      <c r="DS127" s="7"/>
+      <c r="DT127" s="7"/>
+      <c r="DU127" s="7"/>
+      <c r="DV127" s="7"/>
+      <c r="DW127" s="7"/>
+      <c r="DX127" s="7"/>
+      <c r="DY127" s="7"/>
+      <c r="DZ127" s="7"/>
+      <c r="EA127" s="7"/>
+      <c r="EB127" s="7"/>
+      <c r="EC127" s="7"/>
+      <c r="ED127" s="7"/>
+      <c r="EE127" s="7"/>
+      <c r="EF127" s="7"/>
+      <c r="EG127" s="7"/>
+      <c r="EH127" s="7"/>
+      <c r="EI127" s="7"/>
+      <c r="EJ127" s="7"/>
+      <c r="EK127" s="7"/>
+      <c r="EL127" s="7"/>
+      <c r="EM127" s="7"/>
+      <c r="EN127" s="7"/>
+      <c r="EO127" s="7"/>
+      <c r="EP127" s="7"/>
+      <c r="EQ127" s="7"/>
+      <c r="ER127" s="7"/>
+      <c r="ES127" s="7"/>
+      <c r="ET127" s="7"/>
+      <c r="EU127" s="7"/>
+      <c r="EV127" s="7"/>
+      <c r="EW127" s="7"/>
+      <c r="EX127" s="7"/>
+      <c r="EY127" s="7"/>
+      <c r="EZ127" s="7"/>
+      <c r="FA127" s="7"/>
+      <c r="FB127" s="7"/>
+      <c r="FC127" s="7"/>
+      <c r="FD127" s="7"/>
+      <c r="FE127" s="7"/>
+      <c r="FF127" s="7"/>
+      <c r="FG127" s="7"/>
+      <c r="FH127" s="7"/>
+      <c r="FI127" s="7"/>
+      <c r="FJ127" s="7"/>
+      <c r="FK127" s="7"/>
+      <c r="FL127" s="7"/>
+      <c r="FM127" s="7"/>
+      <c r="FN127" s="7"/>
+      <c r="FO127" s="7"/>
+      <c r="FP127" s="7"/>
+      <c r="FQ127" s="7"/>
+      <c r="FR127" s="7"/>
+      <c r="FS127" s="7"/>
+      <c r="FT127" s="7"/>
+      <c r="FU127" s="7"/>
+      <c r="FV127" s="7"/>
+      <c r="FW127" s="7"/>
+      <c r="FX127" s="7"/>
+      <c r="FY127" s="7"/>
+      <c r="FZ127" s="7"/>
+      <c r="GA127" s="7"/>
+      <c r="GB127" s="7"/>
+      <c r="GC127" s="7"/>
+      <c r="GD127" s="7"/>
+      <c r="GE127" s="7"/>
+      <c r="GF127" s="7"/>
+      <c r="GG127" s="7"/>
+      <c r="GH127" s="7"/>
+      <c r="GI127" s="7"/>
+      <c r="GJ127" s="7"/>
+      <c r="GK127" s="7"/>
+      <c r="GL127" s="7"/>
+      <c r="GM127" s="7"/>
+      <c r="GN127" s="7"/>
+      <c r="GO127" s="7"/>
+      <c r="GP127" s="7"/>
+      <c r="GQ127" s="7"/>
+      <c r="GR127" s="7"/>
+      <c r="GS127" s="7"/>
+      <c r="GT127" s="7"/>
+      <c r="GU127" s="7"/>
+      <c r="GV127" s="7"/>
+      <c r="GW127" s="7"/>
+      <c r="GX127" s="7"/>
+      <c r="GY127" s="7"/>
+      <c r="GZ127" s="7"/>
+      <c r="HA127" s="7"/>
+      <c r="HB127" s="7"/>
+      <c r="HC127" s="7"/>
+      <c r="HD127" s="7"/>
+      <c r="HE127" s="7"/>
+      <c r="HF127" s="7"/>
+      <c r="HG127" s="7"/>
+      <c r="HH127" s="7"/>
+      <c r="HI127" s="7"/>
+      <c r="HJ127" s="7"/>
+      <c r="HK127" s="7"/>
+      <c r="HL127" s="7"/>
+      <c r="HM127" s="7"/>
+      <c r="HN127" s="7"/>
+      <c r="HO127" s="7"/>
+      <c r="HP127" s="7"/>
+      <c r="HQ127" s="7"/>
+      <c r="HR127" s="7"/>
+      <c r="HS127" s="7"/>
+      <c r="HT127" s="7"/>
+      <c r="HU127" s="7"/>
+      <c r="HV127" s="7"/>
+      <c r="HW127" s="7"/>
+      <c r="HX127" s="7"/>
+      <c r="HY127" s="7"/>
+      <c r="HZ127" s="7"/>
+      <c r="IA127" s="7"/>
+      <c r="IB127" s="7"/>
+      <c r="IC127" s="7"/>
+      <c r="ID127" s="7"/>
+      <c r="IE127" s="7"/>
+      <c r="IF127" s="7"/>
+      <c r="IG127" s="7"/>
+      <c r="IH127" s="7"/>
+      <c r="II127" s="7"/>
+      <c r="IJ127" s="7"/>
+      <c r="IK127" s="7"/>
+      <c r="IL127" s="7"/>
+      <c r="IM127" s="7"/>
+      <c r="IN127" s="7"/>
+      <c r="IO127" s="7"/>
+      <c r="IP127" s="7"/>
+      <c r="IQ127" s="7"/>
+      <c r="IR127" s="7"/>
+      <c r="IS127" s="7"/>
+      <c r="IT127" s="7"/>
+      <c r="IU127" s="7"/>
+      <c r="IV127" s="7"/>
+      <c r="IW127" s="7"/>
+      <c r="IX127" s="7"/>
+      <c r="IY127" s="7"/>
+      <c r="IZ127" s="7"/>
+      <c r="JA127" s="7"/>
+      <c r="JB127" s="7"/>
+      <c r="JC127" s="7"/>
+      <c r="JD127" s="7"/>
+      <c r="JE127" s="7"/>
+      <c r="JF127" s="7"/>
+      <c r="JG127" s="7"/>
+      <c r="JH127" s="7"/>
+      <c r="JI127" s="7"/>
+      <c r="JJ127" s="7"/>
+      <c r="JK127" s="7"/>
+      <c r="JL127" s="7"/>
+      <c r="JM127" s="7"/>
+      <c r="JN127" s="7"/>
+      <c r="JO127" s="7"/>
+      <c r="JP127" s="7"/>
+      <c r="JQ127" s="7"/>
+      <c r="JR127" s="7"/>
+      <c r="JS127" s="7"/>
+      <c r="JT127" s="7"/>
+      <c r="JU127" s="7"/>
+      <c r="JV127" s="7"/>
+      <c r="JW127" s="7"/>
+      <c r="JX127" s="7"/>
+      <c r="JY127" s="7"/>
+      <c r="JZ127" s="7"/>
+      <c r="KA127" s="7"/>
+      <c r="KB127" s="7"/>
+      <c r="KC127" s="7"/>
+      <c r="KD127" s="7"/>
+      <c r="KE127" s="7"/>
+      <c r="KF127" s="7"/>
+      <c r="KG127" s="7"/>
+      <c r="KH127" s="7"/>
+      <c r="KI127" s="7"/>
+      <c r="KJ127" s="7"/>
+      <c r="KK127" s="7"/>
+      <c r="KL127" s="7"/>
+      <c r="KM127" s="7"/>
+      <c r="KN127" s="7"/>
+      <c r="KO127" s="7"/>
+      <c r="KP127" s="7"/>
+      <c r="KQ127" s="7"/>
+      <c r="KR127" s="7"/>
+      <c r="KS127" s="7"/>
+      <c r="KT127" s="7"/>
+      <c r="KU127" s="7"/>
+      <c r="KV127" s="7"/>
+      <c r="KW127" s="7"/>
+      <c r="KX127" s="7"/>
+      <c r="KY127" s="7"/>
+      <c r="KZ127" s="7"/>
+      <c r="LA127" s="7"/>
+      <c r="LB127" s="7"/>
+      <c r="LC127" s="7"/>
+      <c r="LD127" s="7"/>
+      <c r="LE127" s="7"/>
+      <c r="LF127" s="7"/>
+      <c r="LG127" s="7"/>
+      <c r="LH127" s="7"/>
+      <c r="LI127" s="7"/>
+      <c r="LJ127" s="7"/>
+      <c r="LK127" s="7"/>
+      <c r="LL127" s="7"/>
+      <c r="LM127" s="7"/>
+      <c r="LN127" s="7"/>
+      <c r="LO127" s="7"/>
+      <c r="LP127" s="7"/>
+      <c r="LQ127" s="7"/>
+      <c r="LR127" s="7"/>
+      <c r="LS127" s="7"/>
+      <c r="LT127" s="7"/>
+      <c r="LU127" s="7"/>
+      <c r="LV127" s="7"/>
+      <c r="LW127" s="7"/>
+      <c r="LX127" s="7"/>
+      <c r="LY127" s="7"/>
+      <c r="LZ127" s="7"/>
+      <c r="MA127" s="7"/>
+      <c r="MB127" s="7"/>
+      <c r="MC127" s="7"/>
+      <c r="MD127" s="7"/>
+      <c r="ME127" s="7"/>
+      <c r="MF127" s="7"/>
+      <c r="MG127" s="7"/>
+      <c r="MH127" s="7"/>
+      <c r="MI127" s="7"/>
+      <c r="MJ127" s="7"/>
+      <c r="MK127" s="7"/>
+      <c r="ML127" s="7"/>
+      <c r="MM127" s="7"/>
+      <c r="MN127" s="7"/>
+      <c r="MO127" s="7"/>
+      <c r="MP127" s="7"/>
+      <c r="MQ127" s="7"/>
+      <c r="MR127" s="7"/>
+      <c r="MS127" s="7"/>
+      <c r="MT127" s="7"/>
+      <c r="MU127" s="7"/>
+      <c r="MV127" s="7"/>
+      <c r="MW127" s="7"/>
+      <c r="MX127" s="7"/>
+      <c r="MY127" s="7"/>
+      <c r="MZ127" s="7"/>
+      <c r="NA127" s="7"/>
+      <c r="NB127" s="7"/>
+      <c r="NC127" s="7"/>
+      <c r="ND127" s="7"/>
+      <c r="NE127" s="7"/>
+      <c r="NF127" s="7"/>
+      <c r="NG127" s="7"/>
+      <c r="NH127" s="7"/>
+      <c r="NI127" s="7"/>
+      <c r="NJ127" s="7"/>
+      <c r="NK127" s="7"/>
+      <c r="NL127" s="7"/>
+      <c r="NM127" s="7"/>
+      <c r="NN127" s="7"/>
+      <c r="NO127" s="7"/>
+      <c r="NP127" s="7"/>
+      <c r="NQ127" s="7"/>
+      <c r="NR127" s="7"/>
+      <c r="NS127" s="7"/>
+      <c r="NT127" s="7"/>
+      <c r="NU127" s="7"/>
+      <c r="NV127" s="7"/>
+      <c r="NW127" s="7"/>
+      <c r="NX127" s="7"/>
+      <c r="NY127" s="7"/>
+      <c r="NZ127" s="7"/>
+      <c r="OA127" s="7"/>
+      <c r="OB127" s="7"/>
+      <c r="OC127" s="7"/>
+      <c r="OD127" s="7"/>
+      <c r="OE127" s="7"/>
+      <c r="OF127" s="7"/>
+      <c r="OG127" s="7"/>
+      <c r="OH127" s="7"/>
+      <c r="OI127" s="7"/>
+      <c r="OJ127" s="7"/>
+      <c r="OK127" s="7"/>
+      <c r="OL127" s="7"/>
+      <c r="OM127" s="7"/>
+      <c r="ON127" s="7"/>
+      <c r="OO127" s="7"/>
+      <c r="OP127" s="7"/>
+      <c r="OQ127" s="7"/>
+      <c r="OR127" s="7"/>
+      <c r="OS127" s="7"/>
+      <c r="OT127" s="7"/>
+      <c r="OU127" s="7"/>
+      <c r="OV127" s="7"/>
+      <c r="OW127" s="7"/>
+      <c r="OX127" s="7"/>
+      <c r="OY127" s="7"/>
+      <c r="OZ127" s="7"/>
+      <c r="PA127" s="7"/>
+      <c r="PB127" s="7"/>
+      <c r="PC127" s="7"/>
+      <c r="PD127" s="7"/>
+      <c r="PE127" s="7"/>
+      <c r="PF127" s="7"/>
+      <c r="PG127" s="7"/>
+      <c r="PH127" s="7"/>
+      <c r="PI127" s="7"/>
+      <c r="PJ127" s="7"/>
+      <c r="PK127" s="7"/>
+      <c r="PL127" s="7"/>
+      <c r="PM127" s="7"/>
+      <c r="PN127" s="7"/>
+      <c r="PO127" s="7"/>
+      <c r="PP127" s="7"/>
+      <c r="PQ127" s="7"/>
+      <c r="PR127" s="7"/>
+      <c r="PS127" s="7"/>
+      <c r="PT127" s="7"/>
+      <c r="PU127" s="7"/>
+      <c r="PV127" s="7"/>
+      <c r="PW127" s="7"/>
+      <c r="PX127" s="7"/>
+      <c r="PY127" s="7"/>
+      <c r="PZ127" s="7"/>
+      <c r="QA127" s="7"/>
+      <c r="QB127" s="7"/>
+      <c r="QC127" s="7"/>
+      <c r="QD127" s="7"/>
+      <c r="QE127" s="7"/>
+      <c r="QF127" s="7"/>
+      <c r="QG127" s="7"/>
+      <c r="QH127" s="7"/>
+      <c r="QI127" s="7"/>
+      <c r="QJ127" s="7"/>
+      <c r="QK127" s="7"/>
+      <c r="QL127" s="7"/>
+      <c r="QM127" s="7"/>
+      <c r="QN127" s="7"/>
+      <c r="QO127" s="7"/>
+      <c r="QP127" s="7"/>
+      <c r="QQ127" s="7"/>
+      <c r="QR127" s="7"/>
+      <c r="QS127" s="7"/>
+      <c r="QT127" s="7"/>
+      <c r="QU127" s="7"/>
+      <c r="QV127" s="7"/>
+      <c r="QW127" s="7"/>
+      <c r="QX127" s="7"/>
+      <c r="QY127" s="7"/>
+      <c r="QZ127" s="7"/>
+      <c r="RA127" s="7"/>
+      <c r="RB127" s="7"/>
+      <c r="RC127" s="7"/>
+      <c r="RD127" s="7"/>
+      <c r="RE127" s="7"/>
+      <c r="RF127" s="7"/>
+      <c r="RG127" s="7"/>
+      <c r="RH127" s="7"/>
+      <c r="RI127" s="7"/>
+      <c r="RJ127" s="7"/>
+      <c r="RK127" s="7"/>
+      <c r="RL127" s="7"/>
+      <c r="RM127" s="7"/>
+      <c r="RN127" s="7"/>
+      <c r="RO127" s="7"/>
+      <c r="RP127" s="7"/>
+      <c r="RQ127" s="7"/>
+      <c r="RR127" s="7"/>
+      <c r="RS127" s="7"/>
+      <c r="RT127" s="7"/>
+      <c r="RU127" s="7"/>
+      <c r="RV127" s="7"/>
+      <c r="RW127" s="7"/>
+      <c r="RX127" s="7"/>
+      <c r="RY127" s="7"/>
+      <c r="RZ127" s="7"/>
+      <c r="SA127" s="7"/>
+      <c r="SB127" s="7"/>
+      <c r="SC127" s="7"/>
+      <c r="SD127" s="7"/>
+      <c r="SE127" s="7"/>
+      <c r="SF127" s="7"/>
+      <c r="SG127" s="7"/>
+      <c r="SH127" s="7"/>
+      <c r="SI127" s="7"/>
+      <c r="SJ127" s="7"/>
+      <c r="SK127" s="7"/>
+      <c r="SL127" s="7"/>
+      <c r="SM127" s="7"/>
+      <c r="SN127" s="7"/>
+      <c r="SO127" s="7"/>
+      <c r="SP127" s="7"/>
+      <c r="SQ127" s="7"/>
+      <c r="SR127" s="7"/>
+      <c r="SS127" s="7"/>
+      <c r="ST127" s="7"/>
+      <c r="SU127" s="7"/>
+      <c r="SV127" s="7"/>
+      <c r="SW127" s="7"/>
+      <c r="SX127" s="7"/>
+      <c r="SY127" s="7"/>
+      <c r="SZ127" s="7"/>
+      <c r="TA127" s="7"/>
+      <c r="TB127" s="7"/>
+      <c r="TC127" s="7"/>
+      <c r="TD127" s="7"/>
+      <c r="TE127" s="7"/>
+      <c r="TF127" s="7"/>
+      <c r="TG127" s="7"/>
+      <c r="TH127" s="7"/>
+      <c r="TI127" s="7"/>
+      <c r="TJ127" s="7"/>
+      <c r="TK127" s="7"/>
+      <c r="TL127" s="7"/>
+      <c r="TM127" s="7"/>
+      <c r="TN127" s="7"/>
+      <c r="TO127" s="7"/>
+      <c r="TP127" s="7"/>
+      <c r="TQ127" s="7"/>
+      <c r="TR127" s="7"/>
+      <c r="TS127" s="7"/>
+      <c r="TT127" s="7"/>
+      <c r="TU127" s="7"/>
+      <c r="TV127" s="7"/>
+      <c r="TW127" s="7"/>
+      <c r="TX127" s="7"/>
+      <c r="TY127" s="7"/>
+      <c r="TZ127" s="7"/>
+      <c r="UA127" s="7"/>
+      <c r="UB127" s="7"/>
+      <c r="UC127" s="7"/>
+      <c r="UD127" s="7"/>
+      <c r="UE127" s="7"/>
+      <c r="UF127" s="7"/>
+      <c r="UG127" s="7"/>
+      <c r="UH127" s="7"/>
+      <c r="UI127" s="7"/>
+      <c r="UJ127" s="7"/>
+      <c r="UK127" s="7"/>
+      <c r="UL127" s="7"/>
+      <c r="UM127" s="7"/>
+      <c r="UN127" s="7"/>
+      <c r="UO127" s="7"/>
+      <c r="UP127" s="7"/>
+      <c r="UQ127" s="7"/>
+      <c r="UR127" s="7"/>
+      <c r="US127" s="7"/>
+      <c r="UT127" s="7"/>
+      <c r="UU127" s="7"/>
+      <c r="UV127" s="7"/>
+      <c r="UW127" s="7"/>
+      <c r="UX127" s="7"/>
+      <c r="UY127" s="7"/>
+      <c r="UZ127" s="7"/>
+      <c r="VA127" s="7"/>
+      <c r="VB127" s="7"/>
+      <c r="VC127" s="7"/>
+      <c r="VD127" s="7"/>
+      <c r="VE127" s="7"/>
+      <c r="VF127" s="7"/>
+      <c r="VG127" s="7"/>
+      <c r="VH127" s="7"/>
+      <c r="VI127" s="7"/>
+      <c r="VJ127" s="7"/>
+      <c r="VK127" s="7"/>
+      <c r="VL127" s="7"/>
+      <c r="VM127" s="7"/>
+      <c r="VN127" s="7"/>
+      <c r="VO127" s="7"/>
+      <c r="VP127" s="7"/>
+      <c r="VQ127" s="7"/>
+      <c r="VR127" s="7"/>
+      <c r="VS127" s="7"/>
+      <c r="VT127" s="7"/>
+      <c r="VU127" s="7"/>
+      <c r="VV127" s="7"/>
+      <c r="VW127" s="7"/>
+      <c r="VX127" s="7"/>
+      <c r="VY127" s="7"/>
+      <c r="VZ127" s="7"/>
+      <c r="WA127" s="7"/>
+      <c r="WB127" s="7"/>
+      <c r="WC127" s="7"/>
+      <c r="WD127" s="7"/>
+      <c r="WE127" s="7"/>
+      <c r="WF127" s="7"/>
+      <c r="WG127" s="7"/>
+      <c r="WH127" s="7"/>
+      <c r="WI127" s="7"/>
+      <c r="WJ127" s="7"/>
+      <c r="WK127" s="7"/>
+      <c r="WL127" s="7"/>
+      <c r="WM127" s="7"/>
+      <c r="WN127" s="7"/>
+      <c r="WO127" s="7"/>
+      <c r="WP127" s="7"/>
+      <c r="WQ127" s="7"/>
+      <c r="WR127" s="7"/>
+      <c r="WS127" s="7"/>
+      <c r="WT127" s="7"/>
+      <c r="WU127" s="7"/>
+      <c r="WV127" s="7"/>
+      <c r="WW127" s="7"/>
+      <c r="WX127" s="7"/>
+      <c r="WY127" s="7"/>
+      <c r="WZ127" s="7"/>
+      <c r="XA127" s="7"/>
+      <c r="XB127" s="7"/>
+      <c r="XC127" s="7"/>
+      <c r="XD127" s="7"/>
+      <c r="XE127" s="7"/>
+      <c r="XF127" s="7"/>
+      <c r="XG127" s="7"/>
+      <c r="XH127" s="7"/>
+      <c r="XI127" s="7"/>
+      <c r="XJ127" s="7"/>
+      <c r="XK127" s="7"/>
+      <c r="XL127" s="7"/>
+      <c r="XM127" s="7"/>
+      <c r="XN127" s="7"/>
+      <c r="XO127" s="7"/>
+      <c r="XP127" s="7"/>
+      <c r="XQ127" s="7"/>
+      <c r="XR127" s="7"/>
+      <c r="XS127" s="7"/>
+      <c r="XT127" s="7"/>
+      <c r="XU127" s="7"/>
+      <c r="XV127" s="7"/>
+      <c r="XW127" s="7"/>
+      <c r="XX127" s="7"/>
+      <c r="XY127" s="7"/>
+      <c r="XZ127" s="7"/>
+      <c r="YA127" s="7"/>
+      <c r="YB127" s="7"/>
+      <c r="YC127" s="7"/>
+      <c r="YD127" s="7"/>
+      <c r="YE127" s="7"/>
+      <c r="YF127" s="7"/>
+      <c r="YG127" s="7"/>
+      <c r="YH127" s="7"/>
+      <c r="YI127" s="7"/>
+      <c r="YJ127" s="7"/>
+      <c r="YK127" s="7"/>
+      <c r="YL127" s="7"/>
+      <c r="YM127" s="7"/>
+      <c r="YN127" s="7"/>
+      <c r="YO127" s="7"/>
+      <c r="YP127" s="7"/>
+      <c r="YQ127" s="7"/>
+      <c r="YR127" s="7"/>
+      <c r="YS127" s="7"/>
+      <c r="YT127" s="7"/>
+      <c r="YU127" s="7"/>
+      <c r="YV127" s="7"/>
+      <c r="YW127" s="7"/>
+      <c r="YX127" s="7"/>
+      <c r="YY127" s="7"/>
+      <c r="YZ127" s="7"/>
+      <c r="ZA127" s="7"/>
+      <c r="ZB127" s="7"/>
+      <c r="ZC127" s="7"/>
+      <c r="ZD127" s="7"/>
+      <c r="ZE127" s="7"/>
+      <c r="ZF127" s="7"/>
+      <c r="ZG127" s="7"/>
+      <c r="ZH127" s="7"/>
+      <c r="ZI127" s="7"/>
+      <c r="ZJ127" s="7"/>
+      <c r="ZK127" s="7"/>
+      <c r="ZL127" s="7"/>
+      <c r="ZM127" s="7"/>
+      <c r="ZN127" s="7"/>
+      <c r="ZO127" s="7"/>
+      <c r="ZP127" s="7"/>
+      <c r="ZQ127" s="7"/>
+      <c r="ZR127" s="7"/>
+      <c r="ZS127" s="7"/>
+      <c r="ZT127" s="7"/>
+      <c r="ZU127" s="7"/>
+      <c r="ZV127" s="7"/>
+      <c r="ZW127" s="7"/>
+      <c r="ZX127" s="7"/>
+      <c r="ZY127" s="7"/>
+      <c r="ZZ127" s="7"/>
+      <c r="AAA127" s="7"/>
+      <c r="AAB127" s="7"/>
+      <c r="AAC127" s="7"/>
+      <c r="AAD127" s="7"/>
+      <c r="AAE127" s="7"/>
+      <c r="AAF127" s="7"/>
+      <c r="AAG127" s="7"/>
+      <c r="AAH127" s="7"/>
+      <c r="AAI127" s="7"/>
+      <c r="AAJ127" s="7"/>
+      <c r="AAK127" s="7"/>
+      <c r="AAL127" s="7"/>
+      <c r="AAM127" s="7"/>
+      <c r="AAN127" s="7"/>
+      <c r="AAO127" s="7"/>
+      <c r="AAP127" s="7"/>
+      <c r="AAQ127" s="7"/>
+      <c r="AAR127" s="7"/>
+      <c r="AAS127" s="7"/>
+      <c r="AAT127" s="7"/>
+      <c r="AAU127" s="7"/>
+      <c r="AAV127" s="7"/>
+      <c r="AAW127" s="7"/>
+      <c r="AAX127" s="7"/>
+      <c r="AAY127" s="7"/>
+      <c r="AAZ127" s="7"/>
+      <c r="ABA127" s="7"/>
+      <c r="ABB127" s="7"/>
+      <c r="ABC127" s="7"/>
+      <c r="ABD127" s="7"/>
+      <c r="ABE127" s="7"/>
+      <c r="ABF127" s="7"/>
+      <c r="ABG127" s="7"/>
+      <c r="ABH127" s="7"/>
+      <c r="ABI127" s="7"/>
+      <c r="ABJ127" s="7"/>
+      <c r="ABK127" s="7"/>
+      <c r="ABL127" s="7"/>
+      <c r="ABM127" s="7"/>
+      <c r="ABN127" s="7"/>
+      <c r="ABO127" s="7"/>
+      <c r="ABP127" s="7"/>
+      <c r="ABQ127" s="7"/>
+      <c r="ABR127" s="7"/>
+      <c r="ABS127" s="7"/>
+      <c r="ABT127" s="7"/>
+      <c r="ABU127" s="7"/>
+      <c r="ABV127" s="7"/>
+      <c r="ABW127" s="7"/>
+      <c r="ABX127" s="7"/>
+      <c r="ABY127" s="7"/>
+      <c r="ABZ127" s="7"/>
+      <c r="ACA127" s="7"/>
+      <c r="ACB127" s="7"/>
+      <c r="ACC127" s="7"/>
+      <c r="ACD127" s="7"/>
+      <c r="ACE127" s="7"/>
+      <c r="ACF127" s="7"/>
+      <c r="ACG127" s="7"/>
+      <c r="ACH127" s="7"/>
+      <c r="ACI127" s="7"/>
+      <c r="ACJ127" s="7"/>
+      <c r="ACK127" s="7"/>
+      <c r="ACL127" s="7"/>
+      <c r="ACM127" s="7"/>
+      <c r="ACN127" s="7"/>
+      <c r="ACO127" s="7"/>
+      <c r="ACP127" s="7"/>
+      <c r="ACQ127" s="7"/>
+      <c r="ACR127" s="7"/>
+      <c r="ACS127" s="7"/>
+      <c r="ACT127" s="7"/>
+      <c r="ACU127" s="7"/>
+      <c r="ACV127" s="7"/>
+      <c r="ACW127" s="7"/>
+      <c r="ACX127" s="7"/>
+      <c r="ACY127" s="7"/>
+      <c r="ACZ127" s="7"/>
+      <c r="ADA127" s="7"/>
+      <c r="ADB127" s="7"/>
+      <c r="ADC127" s="7"/>
+      <c r="ADD127" s="7"/>
+      <c r="ADE127" s="7"/>
+      <c r="ADF127" s="7"/>
+      <c r="ADG127" s="7"/>
+      <c r="ADH127" s="7"/>
+      <c r="ADI127" s="7"/>
+      <c r="ADJ127" s="7"/>
+      <c r="ADK127" s="7"/>
+      <c r="ADL127" s="7"/>
+      <c r="ADM127" s="7"/>
+      <c r="ADN127" s="7"/>
+      <c r="ADO127" s="7"/>
+      <c r="ADP127" s="7"/>
+      <c r="ADQ127" s="7"/>
+      <c r="ADR127" s="7"/>
+      <c r="ADS127" s="7"/>
+      <c r="ADT127" s="7"/>
+      <c r="ADU127" s="7"/>
+      <c r="ADV127" s="7"/>
+      <c r="ADW127" s="7"/>
+      <c r="ADX127" s="7"/>
+      <c r="ADY127" s="7"/>
+      <c r="ADZ127" s="7"/>
+      <c r="AEA127" s="7"/>
+      <c r="AEB127" s="7"/>
+      <c r="AEC127" s="7"/>
+      <c r="AED127" s="7"/>
+      <c r="AEE127" s="7"/>
+      <c r="AEF127" s="7"/>
+      <c r="AEG127" s="7"/>
+      <c r="AEH127" s="7"/>
+      <c r="AEI127" s="7"/>
+      <c r="AEJ127" s="7"/>
+      <c r="AEK127" s="7"/>
+      <c r="AEL127" s="7"/>
+      <c r="AEM127" s="7"/>
+      <c r="AEN127" s="7"/>
+      <c r="AEO127" s="7"/>
+      <c r="AEP127" s="7"/>
+      <c r="AEQ127" s="7"/>
+      <c r="AER127" s="7"/>
+      <c r="AES127" s="7"/>
+      <c r="AET127" s="7"/>
+      <c r="AEU127" s="7"/>
+      <c r="AEV127" s="7"/>
+      <c r="AEW127" s="7"/>
+      <c r="AEX127" s="7"/>
+      <c r="AEY127" s="7"/>
+      <c r="AEZ127" s="7"/>
+      <c r="AFA127" s="7"/>
+      <c r="AFB127" s="7"/>
+      <c r="AFC127" s="7"/>
+      <c r="AFD127" s="7"/>
+      <c r="AFE127" s="7"/>
+      <c r="AFF127" s="7"/>
+      <c r="AFG127" s="7"/>
+      <c r="AFH127" s="7"/>
+      <c r="AFI127" s="7"/>
+      <c r="AFJ127" s="7"/>
+      <c r="AFK127" s="7"/>
+      <c r="AFL127" s="7"/>
+      <c r="AFM127" s="7"/>
+      <c r="AFN127" s="7"/>
+      <c r="AFO127" s="7"/>
+      <c r="AFP127" s="7"/>
+      <c r="AFQ127" s="7"/>
+      <c r="AFR127" s="7"/>
+      <c r="AFS127" s="7"/>
+      <c r="AFT127" s="7"/>
+      <c r="AFU127" s="7"/>
+      <c r="AFV127" s="7"/>
+      <c r="AFW127" s="7"/>
+      <c r="AFX127" s="7"/>
+      <c r="AFY127" s="7"/>
+      <c r="AFZ127" s="7"/>
+      <c r="AGA127" s="7"/>
+      <c r="AGB127" s="7"/>
+      <c r="AGC127" s="7"/>
+      <c r="AGD127" s="7"/>
+      <c r="AGE127" s="7"/>
+      <c r="AGF127" s="7"/>
+      <c r="AGG127" s="7"/>
+      <c r="AGH127" s="7"/>
+      <c r="AGI127" s="7"/>
+      <c r="AGJ127" s="7"/>
+      <c r="AGK127" s="7"/>
+      <c r="AGL127" s="7"/>
+      <c r="AGM127" s="7"/>
+      <c r="AGN127" s="7"/>
+      <c r="AGO127" s="7"/>
+      <c r="AGP127" s="7"/>
+      <c r="AGQ127" s="7"/>
+      <c r="AGR127" s="7"/>
+      <c r="AGS127" s="7"/>
+      <c r="AGT127" s="7"/>
+      <c r="AGU127" s="7"/>
+      <c r="AGV127" s="7"/>
+      <c r="AGW127" s="7"/>
+      <c r="AGX127" s="7"/>
+      <c r="AGY127" s="7"/>
+      <c r="AGZ127" s="7"/>
+      <c r="AHA127" s="7"/>
+      <c r="AHB127" s="7"/>
+      <c r="AHC127" s="7"/>
+      <c r="AHD127" s="7"/>
+      <c r="AHE127" s="7"/>
+      <c r="AHF127" s="7"/>
+      <c r="AHG127" s="7"/>
+      <c r="AHH127" s="7"/>
+      <c r="AHI127" s="7"/>
+      <c r="AHJ127" s="7"/>
+      <c r="AHK127" s="7"/>
+      <c r="AHL127" s="7"/>
+      <c r="AHM127" s="7"/>
+      <c r="AHN127" s="7"/>
+      <c r="AHO127" s="7"/>
+      <c r="AHP127" s="7"/>
+      <c r="AHQ127" s="7"/>
+      <c r="AHR127" s="7"/>
+      <c r="AHS127" s="7"/>
+      <c r="AHT127" s="7"/>
+      <c r="AHU127" s="7"/>
+      <c r="AHV127" s="7"/>
+      <c r="AHW127" s="7"/>
+      <c r="AHX127" s="7"/>
+      <c r="AHY127" s="7"/>
+      <c r="AHZ127" s="7"/>
+      <c r="AIA127" s="7"/>
+      <c r="AIB127" s="7"/>
+      <c r="AIC127" s="7"/>
+      <c r="AID127" s="7"/>
+      <c r="AIE127" s="7"/>
+      <c r="AIF127" s="7"/>
+      <c r="AIG127" s="7"/>
+      <c r="AIH127" s="7"/>
+      <c r="AII127" s="7"/>
+      <c r="AIJ127" s="7"/>
+      <c r="AIK127" s="7"/>
+      <c r="AIL127" s="7"/>
+      <c r="AIM127" s="7"/>
+      <c r="AIN127" s="7"/>
+      <c r="AIO127" s="7"/>
+      <c r="AIP127" s="7"/>
+      <c r="AIQ127" s="7"/>
+      <c r="AIR127" s="7"/>
+      <c r="AIS127" s="7"/>
+      <c r="AIT127" s="7"/>
+      <c r="AIU127" s="7"/>
+      <c r="AIV127" s="7"/>
+      <c r="AIW127" s="7"/>
+      <c r="AIX127" s="7"/>
+      <c r="AIY127" s="7"/>
+      <c r="AIZ127" s="7"/>
+      <c r="AJA127" s="7"/>
+      <c r="AJB127" s="7"/>
+      <c r="AJC127" s="7"/>
+      <c r="AJD127" s="7"/>
+      <c r="AJE127" s="7"/>
+      <c r="AJF127" s="7"/>
+      <c r="AJG127" s="7"/>
+      <c r="AJH127" s="7"/>
+      <c r="AJI127" s="7"/>
+      <c r="AJJ127" s="7"/>
+      <c r="AJK127" s="7"/>
+      <c r="AJL127" s="7"/>
+      <c r="AJM127" s="7"/>
+      <c r="AJN127" s="7"/>
+      <c r="AJO127" s="7"/>
+      <c r="AJP127" s="7"/>
+      <c r="AJQ127" s="7"/>
+      <c r="AJR127" s="7"/>
+      <c r="AJS127" s="7"/>
+      <c r="AJT127" s="7"/>
+      <c r="AJU127" s="7"/>
+      <c r="AJV127" s="7"/>
+      <c r="AJW127" s="7"/>
+      <c r="AJX127" s="7"/>
+      <c r="AJY127" s="7"/>
+      <c r="AJZ127" s="7"/>
+      <c r="AKA127" s="7"/>
+      <c r="AKB127" s="7"/>
+      <c r="AKC127" s="7"/>
+      <c r="AKD127" s="7"/>
+      <c r="AKE127" s="7"/>
+      <c r="AKF127" s="7"/>
+      <c r="AKG127" s="7"/>
+      <c r="AKH127" s="7"/>
+      <c r="AKI127" s="7"/>
+      <c r="AKJ127" s="7"/>
+      <c r="AKK127" s="7"/>
+      <c r="AKL127" s="7"/>
+      <c r="AKM127" s="7"/>
+      <c r="AKN127" s="7"/>
+      <c r="AKO127" s="7"/>
+      <c r="AKP127" s="7"/>
+      <c r="AKQ127" s="7"/>
+      <c r="AKR127" s="7"/>
+      <c r="AKS127" s="7"/>
+      <c r="AKT127" s="7"/>
+      <c r="AKU127" s="7"/>
+      <c r="AKV127" s="7"/>
+      <c r="AKW127" s="7"/>
+      <c r="AKX127" s="7"/>
+      <c r="AKY127" s="7"/>
+      <c r="AKZ127" s="7"/>
+      <c r="ALA127" s="7"/>
+      <c r="ALB127" s="7"/>
+      <c r="ALC127" s="7"/>
+      <c r="ALD127" s="7"/>
+      <c r="ALE127" s="7"/>
+      <c r="ALF127" s="7"/>
+      <c r="ALG127" s="7"/>
+      <c r="ALH127" s="7"/>
+      <c r="ALI127" s="7"/>
+      <c r="ALJ127" s="7"/>
+      <c r="ALK127" s="7"/>
+      <c r="ALL127" s="7"/>
+      <c r="ALM127" s="7"/>
+      <c r="ALN127" s="7"/>
+      <c r="ALO127" s="7"/>
+      <c r="ALP127" s="7"/>
+      <c r="ALQ127" s="7"/>
+      <c r="ALR127" s="7"/>
+      <c r="ALS127" s="7"/>
+      <c r="ALT127" s="7"/>
+      <c r="ALU127" s="7"/>
+      <c r="ALV127" s="7"/>
+      <c r="ALW127" s="7"/>
+      <c r="ALX127" s="7"/>
+      <c r="ALY127" s="7"/>
+      <c r="ALZ127" s="7"/>
+      <c r="AMA127" s="7"/>
+      <c r="AMB127" s="7"/>
+      <c r="AMC127" s="7"/>
+      <c r="AMD127" s="7"/>
+      <c r="AME127" s="7"/>
+      <c r="AMF127" s="7"/>
+      <c r="AMG127" s="7"/>
+      <c r="AMH127" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <autoFilter ref="A1:D126" xr:uid="{2A8193EC-26C3-47E8-AA62-347275DAEFB0}"/>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" sqref="A14:A15 B7 B5 B36:B43 B86:B107" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" showErrorMessage="1" sqref="A14:A15 B7 B5 B36:B43 B86:B107 B127:C127" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"integer,decimal,text,binary,locale,boolean,datetime,date"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3855,14 +4916,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D90"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="26" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>235</v>
       </c>
@@ -3876,1138 +4937,1250 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>101</v>
       </c>
-      <c r="C2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>102</v>
       </c>
-      <c r="C3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>103</v>
       </c>
-      <c r="C4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>104</v>
       </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>105</v>
       </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>106</v>
       </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>107</v>
       </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>108</v>
       </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>109</v>
       </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>110</v>
       </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>111</v>
       </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>112</v>
       </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>113</v>
       </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>114</v>
       </c>
-      <c r="C15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>115</v>
       </c>
-      <c r="C16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>116</v>
       </c>
-      <c r="C17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>117</v>
       </c>
-      <c r="C18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>118</v>
       </c>
-      <c r="C19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>119</v>
       </c>
-      <c r="C20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>120</v>
       </c>
-      <c r="C21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <v>121</v>
       </c>
-      <c r="C22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>122</v>
       </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="C23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>123</v>
       </c>
-      <c r="C24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="C24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>124</v>
       </c>
-      <c r="C25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="C25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>125</v>
       </c>
-      <c r="C26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="C26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>126</v>
       </c>
-      <c r="C27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>127</v>
       </c>
-      <c r="C28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="C28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>128</v>
       </c>
-      <c r="C29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="C29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>129</v>
       </c>
-      <c r="C30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="6">
         <v>130</v>
       </c>
-      <c r="C31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>131</v>
       </c>
-      <c r="C32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>132</v>
       </c>
-      <c r="C33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9" t="s">
+      <c r="C33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>1001</v>
       </c>
-      <c r="C34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="C34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>1102</v>
       </c>
-      <c r="C35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+    <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>1103</v>
       </c>
-      <c r="C36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>1104</v>
       </c>
-      <c r="C37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>1201</v>
       </c>
-      <c r="C38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+    <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>1202</v>
       </c>
-      <c r="C39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>1203</v>
       </c>
-      <c r="C40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>1204</v>
       </c>
-      <c r="C41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>1205</v>
       </c>
-      <c r="C42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+    <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>1301</v>
       </c>
-      <c r="C43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="C43" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+    <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>1401</v>
       </c>
-      <c r="C44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="C44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>1402</v>
       </c>
-      <c r="C45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="C45" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+    <row r="46" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>1403</v>
       </c>
-      <c r="C46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+    <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>1404</v>
       </c>
-      <c r="C47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="C47" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+    <row r="48" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <v>1501</v>
       </c>
-      <c r="C48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+    <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <v>1601</v>
       </c>
-      <c r="C49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+    <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <v>1701</v>
       </c>
-      <c r="C50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+    <row r="51" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <v>1801</v>
       </c>
-      <c r="C51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="C51" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+    <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <v>1802</v>
       </c>
-      <c r="C52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+    <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <v>1803</v>
       </c>
-      <c r="C53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+    <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <v>1901</v>
       </c>
-      <c r="C54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="C54" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+    <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>1804</v>
       </c>
-      <c r="C55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="C55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+    <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <v>2101</v>
       </c>
-      <c r="C56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="C56" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+    <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>2201</v>
       </c>
-      <c r="C57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="10" t="s">
+      <c r="C57" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+    <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <v>2301</v>
       </c>
-      <c r="C58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" s="10" t="s">
+      <c r="C58" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+    <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <v>1</v>
       </c>
-      <c r="C59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="10" t="s">
+      <c r="C59" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+    <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <v>2</v>
       </c>
-      <c r="C60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="C60" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+    <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <v>3</v>
       </c>
-      <c r="C61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D61" s="10" t="s">
+      <c r="C61" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+    <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <v>1</v>
       </c>
-      <c r="C62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="C62" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+    <row r="63" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <v>2</v>
       </c>
-      <c r="C63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" s="10" t="s">
+      <c r="C63" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+    <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <v>3</v>
       </c>
-      <c r="C64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="C64" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+    <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>4</v>
       </c>
-      <c r="C65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+    <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>5</v>
       </c>
-      <c r="C66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D66" s="10" t="s">
+      <c r="C66" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+    <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>1</v>
       </c>
-      <c r="C67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" s="10" t="s">
+      <c r="C67" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+    <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>2</v>
       </c>
-      <c r="C68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D68" s="10" t="s">
+      <c r="C68" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
+    <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>3</v>
       </c>
-      <c r="C69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D69" s="10" t="s">
+      <c r="C69" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
+    <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <v>4</v>
       </c>
-      <c r="C70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" s="10" t="s">
+      <c r="C70" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <v>5</v>
       </c>
-      <c r="C71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D71" s="10" t="s">
+      <c r="C71" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
+    <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <v>6</v>
       </c>
-      <c r="C72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D72" s="10" t="s">
+      <c r="C72" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" s="9" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
+    <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <v>1</v>
       </c>
-      <c r="C73" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D73" s="10" t="s">
+      <c r="C73" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
+    <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="9">
         <v>2</v>
       </c>
-      <c r="C74" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="C74" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
+    <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>3</v>
       </c>
-      <c r="C75" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="C75" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" s="9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
+    <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>4</v>
       </c>
-      <c r="C76" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D76" s="10" t="s">
+      <c r="C76" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+    <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <v>5</v>
       </c>
-      <c r="C77" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D77" s="10" t="s">
+      <c r="C77" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+    <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="9">
         <v>6</v>
       </c>
-      <c r="C78" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D78" s="10" t="s">
+      <c r="C78" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+    <row r="79" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="10">
-        <v>0</v>
-      </c>
-      <c r="C79" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" s="10" t="s">
+      <c r="B79" s="9">
+        <v>0</v>
+      </c>
+      <c r="C79" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
+    <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="9">
         <v>1</v>
       </c>
-      <c r="C80" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" s="10" t="s">
+      <c r="C80" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
+    <row r="81" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <v>1</v>
       </c>
-      <c r="C81" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D81" s="10" t="s">
+      <c r="C81" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="10" t="s">
+    <row r="82" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="10">
-        <v>0</v>
-      </c>
-      <c r="C82" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" s="10" t="s">
+      <c r="B82" s="9">
+        <v>0</v>
+      </c>
+      <c r="C82" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>305</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B83" s="11">
+        <v>30</v>
+      </c>
+      <c r="C83" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B84" s="11">
+        <v>23</v>
+      </c>
+      <c r="C84" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B85" s="11">
+        <v>22</v>
+      </c>
+      <c r="C85" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B86" s="11">
+        <v>21</v>
+      </c>
+      <c r="C86" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B87" s="11">
+        <v>13</v>
+      </c>
+      <c r="C87" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B88" s="11">
+        <v>12</v>
+      </c>
+      <c r="C88" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B89" s="11">
+        <v>11</v>
+      </c>
+      <c r="C89" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B90" s="11">
+        <v>10</v>
+      </c>
+      <c r="C90" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
